--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.21689897740279</v>
+        <v>6.535246083827954</v>
       </c>
       <c r="D2" t="n">
-        <v>40.05756032718263</v>
+        <v>6.509353553167177</v>
       </c>
       <c r="E2" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F2" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.3342263687348</v>
+        <v>5.904311784919405</v>
       </c>
       <c r="D3" t="n">
-        <v>36.25977178437053</v>
+        <v>5.892212914960211</v>
       </c>
       <c r="E3" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F3" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.2671574169836</v>
+        <v>5.730913080259835</v>
       </c>
       <c r="D4" t="n">
-        <v>35.30995449239109</v>
+        <v>5.737867605013553</v>
       </c>
       <c r="E4" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F4" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.88544473445999</v>
+        <v>5.506384769349748</v>
       </c>
       <c r="D5" t="n">
-        <v>33.65733193126107</v>
+        <v>5.469316438829924</v>
       </c>
       <c r="E5" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F5" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.89766309844064</v>
+        <v>6.808370253496604</v>
       </c>
       <c r="D6" t="n">
-        <v>42.03174472768277</v>
+        <v>6.83015851824845</v>
       </c>
       <c r="E6" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F6" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.44264058864113</v>
+        <v>3.646929095654183</v>
       </c>
       <c r="D7" t="n">
-        <v>22.18738920274156</v>
+        <v>3.605450745445504</v>
       </c>
       <c r="E7" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F7" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.16466626526286</v>
+        <v>2.139258268105215</v>
       </c>
       <c r="D8" t="n">
-        <v>13.28460919909229</v>
+        <v>2.158748994852497</v>
       </c>
       <c r="E8" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F8" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.8880892659415</v>
+        <v>6.481814505715493</v>
       </c>
       <c r="D9" t="n">
-        <v>39.64089787275142</v>
+        <v>6.441645904322105</v>
       </c>
       <c r="E9" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F9" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.06269766090691</v>
+        <v>6.510188369897373</v>
       </c>
       <c r="D10" t="n">
-        <v>40.2747231596553</v>
+        <v>6.544642513443987</v>
       </c>
       <c r="E10" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F10" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.00125952324802</v>
+        <v>7.475204672527803</v>
       </c>
       <c r="D11" t="n">
-        <v>45.77930326341236</v>
+        <v>7.439136780304509</v>
       </c>
       <c r="E11" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F11" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.85223998318295</v>
+        <v>5.500988997267229</v>
       </c>
       <c r="D12" t="n">
-        <v>33.650677839836</v>
+        <v>5.46823514897335</v>
       </c>
       <c r="E12" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F12" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.15691424122357</v>
+        <v>6.36299856419883</v>
       </c>
       <c r="D13" t="n">
-        <v>38.98888717160081</v>
+        <v>6.335694165385132</v>
       </c>
       <c r="E13" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F13" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.081069576946</v>
+        <v>5.050673806253725</v>
       </c>
       <c r="D14" t="n">
-        <v>30.9943641976529</v>
+        <v>5.036584182118596</v>
       </c>
       <c r="E14" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F14" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.17917364965522</v>
+        <v>6.529115718068973</v>
       </c>
       <c r="D15" t="n">
-        <v>40.05839312132921</v>
+        <v>6.509488882215997</v>
       </c>
       <c r="E15" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F15" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.31571584512941</v>
+        <v>4.60130382483353</v>
       </c>
       <c r="D16" t="n">
-        <v>20.12881314966821</v>
+        <v>3.270932136821084</v>
       </c>
       <c r="E16" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F16" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.72196242623941</v>
+        <v>4.342318894263904</v>
       </c>
       <c r="D17" t="n">
-        <v>16.76619813365456</v>
+        <v>2.724507196718867</v>
       </c>
       <c r="E17" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F17" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>44.22788099429403</v>
+        <v>7.18703066157278</v>
       </c>
       <c r="D18" t="n">
-        <v>36.39234810862411</v>
+        <v>5.913756567651418</v>
       </c>
       <c r="E18" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F18" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>42.8027975553855</v>
+        <v>6.955454602750144</v>
       </c>
       <c r="D19" t="n">
-        <v>26.14395854313366</v>
+        <v>4.248393263259219</v>
       </c>
       <c r="E19" t="n">
-        <v>8.169221275107558</v>
+        <v>1.327498457204978</v>
       </c>
       <c r="F19" t="n">
-        <v>9.102048444594903</v>
+        <v>1.479082872246672</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
